--- a/cases/spreadsheetbench_working_paper_transpose_hard/data/workbooks/working_paper_variant_c.xlsx
+++ b/cases/spreadsheetbench_working_paper_transpose_hard/data/workbooks/working_paper_variant_c.xlsx
@@ -4,7 +4,9 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15"/>
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\study\VBA\VBA_attachments\VBA_attachments\vba泛化_0522_陈庆贺\vba泛化_0522_陈庆贺\581-46\"/>
+    </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B1AA83-8498-4079-8A19-7792C5C391F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
